--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>1.11</v>
+        <v>0.66</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.12</v>
+        <v>0.62</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.11</v>
+        <v>0.43</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.43</v>
+        <v>1.11</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.65</v>
+        <v>1.01</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.86</v>
+        <v>1.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.11</v>
+        <v>0.66</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.04</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.47</v>
+        <v>1.01</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.12</v>
+        <v>0.62</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.54</v>
+        <v>1.06</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.91</v>
+        <v>0.58</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.74</v>
+        <v>0.62</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.14</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.45</v>
+        <v>0.98</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.64</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.44</v>
+        <v>1.11</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.15</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.47</v>
+        <v>1.06</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.78</v>
+        <v>1.11</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.68</v>
+        <v>1.01</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.66</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.79</v>
+        <v>1.12</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.11</v>
+        <v>0.43</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.46</v>
+        <v>1.04</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.43</v>
+        <v>1.11</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.6</v>
+        <v>0.86</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.1</v>
+        <v>0.45</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.44</v>
+        <v>0.66</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.42</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.43</v>
+        <v>0.83</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>1.07</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>1.07</v>
+        <v>0.7</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.07</v>
+        <v>0.59</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.84</v>
+        <v>1.06</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1.08</v>
+        <v>0.91</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.89</v>
+        <v>0.74</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.13</v>
+        <v>0.46</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.49</v>
+        <v>1.15</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.95</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.1</v>
+        <v>0.66</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.15</v>
+        <v>0.5</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.14</v>
+        <v>0.61</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.55</v>
+        <v>1.11</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.84</v>
+        <v>1.08</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.97</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.01</v>
+        <v>0.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.49</v>
+        <v>0.73</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.14</v>
+        <v>0.61</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.55</v>
+        <v>1.11</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.78</v>
+        <v>1.13</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1.11</v>
+        <v>0.64</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.65</v>
+        <v>1.13</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1.14</v>
+        <v>0.54</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.65</v>
+        <v>1.14</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.1</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.47</v>
+        <v>1.02</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.48</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1.11</v>
+        <v>0.51</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1.01</v>
+        <v>0.66</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.63</v>
+        <v>1.04</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.06</v>
+        <v>0.7</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.59</v>
+        <v>1.01</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.63</v>
+        <v>0.49</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.13</v>
+        <v>0.57</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.64</v>
+        <v>0.99</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.58</v>
+        <v>0.48</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.11</v>
+        <v>0.5</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.89</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.67</v>
+        <v>0.48</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.46</v>
+        <v>1.02</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.05</v>
+        <v>0.48</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.13</v>
+        <v>0.52</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.95</v>
+        <v>0.52</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>1.07</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.72</v>
+        <v>1.07</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>1.07</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.68</v>
+        <v>0.79</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.88</v>
+        <v>1.07</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.87</v>
+        <v>0.42</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.91</v>
+        <v>1.15</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1.14</v>
+        <v>0.46</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.7</v>
+        <v>1.03</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.97</v>
+        <v>0.58</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>0.49</v>
+        <v>1.08</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.58</v>
+        <v>1.06</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.76</v>
+        <v>0.44</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.02</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.84</v>
+        <v>0.64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.72</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.07</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.59</v>
+        <v>0.47</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.51</v>
+        <v>1.13</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.06</v>
+        <v>0.62</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.91</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.49</v>
+        <v>0.9</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.14</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.72</v>
+        <v>1.13</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.98</v>
+        <v>0.65</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.15</v>
+        <v>0.55</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.68</v>
+        <v>0.55</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.78</v>
+        <v>1.03</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.7</v>
+        <v>1.03</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1.14</v>
+        <v>0.52</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.7</v>
+        <v>1.08</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.67</v>
+        <v>0.91</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.51</v>
+        <v>0.98</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.66</v>
+        <v>0.98</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.42</v>
+        <v>0.74</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.55</v>
+        <v>0.96</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.97</v>
+        <v>0.58</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.14</v>
+        <v>0.64</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.51</v>
+        <v>1.11</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.08</v>
+        <v>0.67</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.13</v>
+        <v>0.62</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.42</v>
+        <v>1.08</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.43</v>
+        <v>1.05</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>1.07</v>
+        <v>0.54</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.64</v>
+        <v>1.11</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.54</v>
+        <v>1.09</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1.12</v>
+        <v>0.57</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.54</v>
+        <v>1.08</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.57</v>
+        <v>1.13</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.49</v>
+        <v>1.08</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.73</v>
+        <v>1.14</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.58</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.48</v>
+        <v>0.8</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>1.08</v>
+        <v>0.52</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.46</v>
+        <v>0.79</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1.13</v>
+        <v>0.55</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.72</v>
+        <v>0.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.06</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.67</v>
+        <v>1.01</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.76</v>
+        <v>0.98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.13</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.46</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.98</v>
+        <v>0.45</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1.13</v>
+        <v>0.68</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.59</v>
+        <v>1.02</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>1.04</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.05</v>
+        <v>0.44</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.57</v>
+        <v>1.02</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.92</v>
+        <v>1.02</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.12</v>
+        <v>0.45</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.84</v>
+        <v>0.66</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.96</v>
+        <v>0.51</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.85</v>
+        <v>0.52</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.53</v>
+        <v>0.66</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.84</v>
+        <v>0.68</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.65</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.5</v>
+        <v>0.91</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.49</v>
+        <v>1.1</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1.14</v>
+        <v>0.62</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1.06</v>
+        <v>0.55</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.62</v>
+        <v>0.43</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.59</v>
+        <v>0.89</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.48</v>
+        <v>1.1</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.98</v>
+        <v>0.59</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1.08</v>
+        <v>0.64</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.42</v>
+        <v>1.12</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.9</v>
+        <v>0.46</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>1.05</v>
+        <v>0.62</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.1</v>
+        <v>0.93</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.53</v>
+        <v>1.1</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.44</v>
+        <v>1.09</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="G167" s="2" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>0.51</v>
+        <v>1.09</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>1.14</v>
+        <v>0.48</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>1.13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.84</v>
+        <v>1.01</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.01</v>
+        <v>0.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
+        <v>0.43</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.1</v>
+        <v>0.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.53</v>
+        <v>1.1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.93</v>
+        <v>1.12</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1.04</v>
+        <v>0.44</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.99</v>
+        <v>1.14</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.1</v>
+        <v>0.87</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.44</v>
+        <v>1.09</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.55</v>
+        <v>0.87</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.45</v>
+        <v>1.06</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.96</v>
+        <v>0.7</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.82</v>
+        <v>0.47</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.47</v>
+        <v>0.98</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.43</v>
+        <v>0.92</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.14</v>
+        <v>0.78</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1.15</v>
+        <v>0.57</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.49</v>
+        <v>0.97</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.87</v>
+        <v>1.13</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.65</v>
+        <v>1.15</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.46</v>
+        <v>1.15</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.87</v>
+        <v>0.43</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.51</v>
+        <v>1.09</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.68</v>
+        <v>1.08</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.7</v>
+        <v>0.96</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.68</v>
+        <v>1.05</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.97</v>
+        <v>1.08</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1.14</v>
+        <v>0.48</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.91</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1.02</v>
+        <v>0.42</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.48</v>
+        <v>0.78</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.82</v>
+        <v>0.54</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>1.07</v>
+        <v>0.44</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.93</v>
+        <v>0.65</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.44</v>
+        <v>0.67</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>1.09</v>
+        <v>0.87</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.82</v>
+        <v>0.46</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>1.05</v>
+        <v>0.61</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.42</v>
+        <v>1.05</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.99</v>
+        <v>0.68</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -4322,7 +4322,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.12</v>
+        <v>0.84</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -6700,7 +6700,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="G153" s="2" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G155" s="2" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="G157" s="2" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1.15</v>
+        <v>0.53</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="G159" s="2" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="G161" s="2" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="G169" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="G171" s="2" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="G173" s="2" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="G175" s="2" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="G177" s="2" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="G179" s="2" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="G181" s="2" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="G183" s="2" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="G185" s="2" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="G187" s="2" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="G189" s="2" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -8258,7 +8258,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="G191" s="2" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="G193" s="2" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="G195" s="2" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="G197" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="G199" s="2" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="G203" s="2" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="G205" s="2" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="G207" s="2" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="G209" s="2" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="G211" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="G213" s="2" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -9242,7 +9242,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="G215" s="2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G217" s="2" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="G219" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G221" s="2" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="G223" s="2" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="G225" s="2" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="G227" s="2" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="G229" s="2" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -9939,7 +9939,7 @@
         </is>
       </c>
       <c r="G231" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -9980,7 +9980,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="G233" s="2" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="G237" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -10267,7 +10267,7 @@
         </is>
       </c>
       <c r="G239" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -10349,7 +10349,7 @@
         </is>
       </c>
       <c r="G241" s="2" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="G243" s="2" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="G245" s="2" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="G247" s="2" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="G249" s="2" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="G251" s="2" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="G253" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="G255" s="2" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="G257" s="2" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="G259" s="2" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="G261" s="2" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="G263" s="2" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G265" s="2" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="G267" s="2" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="G269" s="2" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="G271" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -11661,7 +11661,7 @@
         </is>
       </c>
       <c r="G273" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="G275" s="2" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="G277" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="G279" s="2" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G281" s="2" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -12112,7 +12112,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="G285" s="2" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G287" s="2" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="G289" s="2" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="G291" s="2" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         </is>
       </c>
       <c r="G293" s="2" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -12563,7 +12563,7 @@
         </is>
       </c>
       <c r="G295" s="2" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G297" s="2" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="G299" s="2" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -12768,7 +12768,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="G301" s="2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.54</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12993,7 +12993,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.13</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -13239,7 +13239,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.01</v>
+        <v>0.44</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13567,7 +13567,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13649,7 +13649,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -13772,7 +13772,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.93</v>
+        <v>0.46</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.93</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.89</v>
+        <v>0.47</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -14100,7 +14100,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -14264,7 +14264,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.05</v>
+        <v>0.43</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -14305,7 +14305,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.12</v>
+        <v>0.53</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.04</v>
+        <v>0.54</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -14592,7 +14592,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.65</v>
+        <v>1.06</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -14756,7 +14756,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -14838,7 +14838,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -14879,7 +14879,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.53</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.63</v>
+        <v>1.12</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.53</v>
+        <v>0.98</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.44</v>
+        <v>0.84</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -15740,7 +15740,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -15904,7 +15904,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15986,7 +15986,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.45</v>
+        <v>0.89</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.13</v>
+        <v>0.53</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16314,7 +16314,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.66</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16601,7 +16601,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.99</v>
+        <v>0.68</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.6</v>
+        <v>1.01</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -16683,7 +16683,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1.09</v>
+        <v>0.88</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -16765,7 +16765,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.76</v>
+        <v>1.1</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1.14</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -17011,7 +17011,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.47</v>
+        <v>0.99</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -17175,7 +17175,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -17216,7 +17216,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -17298,7 +17298,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.89</v>
+        <v>0.53</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -17421,7 +17421,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -17544,7 +17544,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17585,7 +17585,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.9</v>
+        <v>1.11</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17749,7 +17749,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1.13</v>
+        <v>0.49</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.83</v>
+        <v>0.61</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1.13</v>
+        <v>0.54</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18036,7 +18036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.89</v>
+        <v>1.14</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -18118,7 +18118,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -18159,7 +18159,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.47</v>
+        <v>0.93</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -18200,7 +18200,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -18323,7 +18323,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.67</v>
+        <v>0.43</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -18405,7 +18405,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -18610,7 +18610,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -18651,7 +18651,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.8</v>
+        <v>1.09</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18774,7 +18774,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18815,7 +18815,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18856,7 +18856,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18979,7 +18979,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -19020,7 +19020,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1.12</v>
+        <v>0.84</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19184,7 +19184,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1.15</v>
+        <v>0.53</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.48</v>
+        <v>1.06</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -19430,7 +19430,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -19471,7 +19471,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -19512,7 +19512,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -19553,7 +19553,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1.03</v>
+        <v>0.63</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.99</v>
+        <v>0.53</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.96</v>
+        <v>0.54</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -19799,7 +19799,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.49</v>
+        <v>0.87</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -19922,7 +19922,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -20168,7 +20168,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -20209,7 +20209,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.75</v>
+        <v>0.43</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1.08</v>
+        <v>0.47</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -20578,7 +20578,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -20660,7 +20660,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.82</v>
+        <v>0.61</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -20783,7 +20783,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -20988,7 +20988,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -21029,7 +21029,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -21070,7 +21070,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -21111,7 +21111,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -21152,7 +21152,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -21193,7 +21193,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -21316,7 +21316,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>0.51</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -21562,7 +21562,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -21644,7 +21644,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -21685,7 +21685,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -21767,7 +21767,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -21890,7 +21890,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -22013,7 +22013,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -22095,7 +22095,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -22136,7 +22136,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.47</v>
+        <v>1.15</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -22218,7 +22218,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -22341,7 +22341,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -22505,7 +22505,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -22546,7 +22546,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1.15</v>
+        <v>0.83</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -22628,7 +22628,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.54</v>
+        <v>0.97</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -22751,7 +22751,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -22792,7 +22792,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -22833,7 +22833,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -22915,7 +22915,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.84</v>
+        <v>0.71</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.48</v>
+        <v>0.99</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -23079,7 +23079,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -23202,7 +23202,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.55</v>
+        <v>1.07</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.98</v>
+        <v>0.79</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.44</v>
+        <v>0.77</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -23489,7 +23489,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23653,7 +23653,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -23694,7 +23694,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -23858,7 +23858,7 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -23981,7 +23981,7 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -24022,7 +24022,7 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24063,7 +24063,7 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -24104,7 +24104,7 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -24309,7 +24309,7 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -24391,7 +24391,7 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -24473,7 +24473,7 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>1.04</v>
+        <v>0.75</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -24514,7 +24514,7 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.95</v>
+        <v>0.71</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -24596,7 +24596,7 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24719,7 +24719,7 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>P3 - Low</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24760,7 +24760,7 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>P1 - High</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P3 - Low</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>P2 - Medium</t>
+          <t>P0 - Critical</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -25088,7 +25088,7 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>P0 - Critical</t>
+          <t>P2 - Medium</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -25129,7 +25129,7 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
